--- a/Tests/Integrated Tests/integrated_tests.xlsx
+++ b/Tests/Integrated Tests/integrated_tests.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mortrpestl\Desktop\Archives\mortrpestl\The UPper Hand\1st Year\1st Sem\CS11\cs11project\cs11-project-jugemu-jugemu\Tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mortrpestl\Desktop\Archives\mortrpestl\The UPper Hand\1st Year\1st Sem\CS11\cs11project\cs11-project-jugemu-jugemu\Tests\Integrated Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6558C0-5ADC-43A7-A2ED-8781F9910064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3A8AA2-04A0-4F18-93A2-F9A216A60A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="341">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -3898,7 +3898,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4205,7 +4205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="5"/>
@@ -6097,11 +6097,6 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Tests/Integrated Tests/integrated_tests.xlsx
+++ b/Tests/Integrated Tests/integrated_tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mortrpestl\Desktop\Archives\mortrpestl\The UPper Hand\1st Year\1st Sem\CS11\cs11project\cs11-project-jugemu-jugemu\Tests\Integrated Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3A8AA2-04A0-4F18-93A2-F9A216A60A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1CC34A-5F43-4EE4-B2B7-1E5444DDDA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="340">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -3596,22 +3596,7 @@
     <t>71</t>
   </si>
   <si>
-    <t>Attempt to move after reset in the same string</t>
-  </si>
-  <si>
     <t>ww!aaaaaaaaaaa</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T..................T
-T..................T
-T.....~....+.+.....T
-T.....~......+.....T
-T.....~............T
-T..........L.......T
-T..................T
-TTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>72</t>
@@ -3817,6 +3802,9 @@
 T........T
 T......~.T
 TTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>Attempt to move after reset in the same string (should still run)</t>
   </si>
 </sst>
 </file>
@@ -4240,7 +4228,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
@@ -4257,7 +4245,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>
@@ -5427,7 +5415,7 @@
         <v>218</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>219</v>
@@ -5939,16 +5927,16 @@
         <v>307</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>292</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="4">
@@ -5960,19 +5948,19 @@
         <v>254</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>292</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="4">
@@ -5981,22 +5969,22 @@
     </row>
     <row r="74" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="F74" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="4">
@@ -6005,22 +5993,22 @@
     </row>
     <row r="75" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="4">
@@ -6029,22 +6017,22 @@
     </row>
     <row r="76" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="4">
@@ -6053,22 +6041,22 @@
     </row>
     <row r="77" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B77" s="5">
         <v>76</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="E77" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>338</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H77" s="4">
         <v>45962</v>
@@ -6076,22 +6064,22 @@
     </row>
     <row r="78" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B78" s="5">
         <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>337</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H78" s="4">
         <v>45962</v>

--- a/Tests/Integrated Tests/integrated_tests.xlsx
+++ b/Tests/Integrated Tests/integrated_tests.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mortrpestl\Desktop\Archives\mortrpestl\The UPper Hand\1st Year\1st Sem\CS11\cs11project\cs11-project-jugemu-jugemu\Tests\Integrated Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1CC34A-5F43-4EE4-B2B7-1E5444DDDA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEBDBBC-F76A-4602-B43C-7052C3FDDAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -68,36 +81,10 @@
     <t>ddddddddddddddddddddd</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x..*.L.T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>Movement to tree</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x..*..LT
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>3</t>
@@ -108,19 +95,6 @@
   <si>
     <t>dwwd
 ssssssssssssss</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~..T
-T.*.._.....x..*..LT
-T.......R....R*..RT
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>4</t>
@@ -140,19 +114,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTLTTTTTT
-T....+R..T+.......T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x..*...T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -164,19 +125,6 @@
 d
 s
 s</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x......T
-T.......R....R*...T
-T..........._.*L.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>6</t>
@@ -209,19 +157,6 @@
 d
 d
 d</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-....L..............
-.....+R...+....x...
-.~...x*._..R.......
-..~_.*...+.....~.R.
-..*.._.....x.......
-........R....R*....
-............_.*T.R.
-.R._.~..R.x*...RR..
-.R....~..._........
-...................</t>
   </si>
   <si>
     <t>7</t>
@@ -236,19 +171,6 @@
 wwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaassssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssdddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddddwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwww</t>
   </si>
   <si>
-    <t>NO CLEAR
-..................L
-.....+R...+....x...
-.~...x*._..R.......
-..~_.*...+.....~.R.
-..*.._.....x.......
-........R....R*....
-............_.*T.R.
-.R._.~..R.x*...RR..
-.R....~..._........
-...................</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -371,19 +293,6 @@
 ass</t>
   </si>
   <si>
-    <t>CLEAR
-...................
-......R........x...
-.~...x*R_..........
-..~_.*...L.....~.R.
-..*.._.....x..*....
-............RR*....
-............_.*T.R.
-.R._.~..R......RR..
-.R....~..._........
-...................</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -399,19 +308,6 @@
 s</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T.....x..T
-T~...x*._.LR......T
-TT~_.*...+.....~.RT
-T.*.._.....x..*...T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -435,19 +331,6 @@
 d</t>
   </si>
   <si>
-    <t>CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....LR..T.....x..T
-T~...x*._..R......T
-TT~_.*.........~.RT
-T.*.._.....x..*...T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -479,19 +362,6 @@
 s</t>
   </si>
   <si>
-    <t>NO CLEAR
-...................
-.....+R...+....x...
-.~...x*._..R.......
-..~_.*...+.....~.R.
-..*.._.....x....L..
-........R....R*....
-............_.*T.R.
-.R._.~..R.x*...RR..
-.R....~..._........
-...................</t>
-  </si>
-  <si>
     <t>Flamethrower</t>
   </si>
   <si>
@@ -509,19 +379,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x......T
-T.......R....R*...T
-T..........._.*.LRT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -539,19 +396,6 @@
 s</t>
   </si>
   <si>
-    <t>NO CLEAR
-...................
-.....+R...+...Lx...
-.~...x*._..R.......
-..~_.*...+.....~.R.
-..*.._.....x.......
-........R....R*....
-............_.*T.R.
-.R._.~..R.x*...RR..
-.R....~..._........
-...................</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -570,19 +414,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x......T
-T.......R....R*..LT
-T..........._.*..RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
@@ -609,19 +440,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-...................
-.....+R...+....x...
-.~...x*._..R.......
-..~_.*...+.....~.R.
-..*.._.....x.......
-........R....R....L
-............_.*..R.
-.R._.~..R.x*...RR..
-.R....~..._........
-...................</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -636,19 +454,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....xL.....T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -672,19 +477,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+R...x..T
-T~...x*._..L......T
-TT~_.*...+.....~.RT
-T.*.._.....x......T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -706,19 +498,6 @@
 s
 d
 d</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+....x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x...L..T
-T.......R....R*...T
-T..........._.*T.RT
-TR._.~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>Mushroom</t>
@@ -832,19 +611,6 @@
 s</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T.....R..T.....x..T
-T~...x*._..R......T
-TT~_.*.........~.RT
-T.*.._.....x..*...T
-T..~~~..R....R*...T
-T..~+~......_.*T.RT
-TR.~~~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -881,19 +647,6 @@
 a
 d
 d</t>
-  </si>
-  <si>
-    <t>CLEAR
-TTTTTTTTTTTTTTTTTTT
-T.....R..T.....x..T
-T~...x*._..R......T
-TT~_.*.........~.RT
-T.*.._.....x..*...T
-T..~~~.......R*...T
-T..~L_......_.*T.RT
-TR.~~~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>PavedTile</t>
@@ -910,19 +663,6 @@
 aaaa
 sssssssss
 wwwwwww</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTT
-T....+R..T+.L..x..T
-T~...x*._..R......T
-TT~_.*...+.....~.RT
-T.*.._.....x..*...T
-T..~~~..R....R*...T
-T..~+~......_.*T.RT
-TR.~~~..R.x*...RR.T
-TR....~T.T_.......T
-TTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>24</t>
@@ -961,23 +701,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTT
-T..x....T.R.._..+T~.....T
-T.T.....~.R........T.+.~T
-T...T.Tx....~.....R.T..*T
-T.....*....T...T.T..~.TTT
-T.......T....+....._~._.T
-T....~....+......R......T
-T*.T..__...___.L..~_.*~.T
-T.x....+..R.T.........T.T
-T....+_....+.......T.T.TT
-T_T..........T.._T.....*T
-T.....+...*R~...*...+...T
-T........T...+TxR.T...T.T
-TTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -1012,23 +735,6 @@
 d
 w
 w</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTT
-T..x....T.R.._..+T~.....T
-T.T.....~.R........T.+.~T
-T...T.Tx....~.....R.T..*T
-T.....*....T...T.T..~.TTT
-T.......T....+....._~._.T
-T....~....+........L....T
-T*.T..__...___....__.*~.T
-T.x....+..R.T.........T.T
-T....+_....+.......T.T.TT
-T_T..........T.._T.....*T
-T.....+...*R~...*...+...T
-T........T...+TxR.T...T.T
-TTTTTTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>26</t>
@@ -1128,23 +834,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTT
-T..x....T.R.._..+T~.....T
-T.T.....~..........T.+.~T
-T...T.Tx....~.......T..*T
-T.....*....T...T.T.._.TTT
-T.......T....+.....__._.T
-T....~....+.............T
-T*.T..__...___....__L*~.T
-T.x....+..R.T.........T.T
-T....+_....+.......T.T.TT
-T_T..........T.._T.....*T
-T.....+...*R~...*...+...T
-T........T...+TxR.T...T.T
-TTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>Axe</t>
   </si>
   <si>
@@ -1162,23 +851,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTT
-T..x....T.R.._..+T~.....T
-T.T.....~.R........T.+.~T
-T...T.Tx....~.....R.T..*T
-T.....*....T...T.T..~.TTT
-T..L....T....+....._~._.T
-T....~....+......R......T
-T*....__...___....~_.*~.T
-T......+..R.T.........T.T
-T....+_....+.......T.T.TT
-T_T..........T.._T.....*T
-T.....+...*R~...*...+...T
-T........T...+TxR.T...T.T
-TTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
@@ -1218,23 +890,6 @@
 d
 w
 s</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTT
-T..x....T.R.._..+T~.....T
-T.T.....~.R........T.+.~T
-T...T.Tx....~.....R.T..*T
-T.....*....T...T.T..~.LTT
-T.......T....+....._~._.T
-T....~....+......R......T
-T*.T..__...___....~_.*~.T
-T......+..R.T.........T.T
-T....+_....+.......T.T.TT
-T_T..........T.._T.....*T
-T.....+...*R~...*...+...T
-T........T...+TxR.T...T.T
-TTTTTTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>Rock</t>
@@ -1281,20 +936,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R...........T
-T.......R.....R.....T
-T.....R..R....R...R.T
-TR..........L.......T
-T........._..*......T
-TR..Rx~...R*R...__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -1317,20 +958,6 @@
 d
 w
 aaaaaaaa</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R...........T
-T.......R.....RRL...T
-T.....R..R.R......R.T
-TR..................T
-T........._..*......T
-TR..Rx~...R*....__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>31</t>
@@ -1358,20 +985,6 @@
 wwww</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R...........T
-T...R...R.....R.....T
-T...L....R.R..R...R.T
-TR..................T
-T........._..*......T
-TR..Rx~...R*....__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>32</t>
   </si>
   <si>
@@ -1396,20 +1009,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R...........T
-T.......R.....R.....T
-T....L...R.R..R...R.T
-TR..................T
-T....R...._..*......T
-TR..Rx~...R*....__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>33</t>
   </si>
   <si>
@@ -1433,20 +1032,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R.....R.....T
-T.......R....L......T
-T.....R..R.R......R.T
-TR...........R......T
-T........._..*......T
-TR..Rx~...R*....__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>34</t>
   </si>
   <si>
@@ -1475,20 +1060,6 @@
 a</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R...........T
-T.......R...........T
-T.....R..R.R.R....R.T
-TR..................T
-T........._..*......T
-TR..Rx~...R*..L.R_~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>35</t>
   </si>
   <si>
@@ -1526,20 +1097,6 @@
 a
 s
 s</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R...........T
-T.......R.....R.....T
-T.....R..R.R......R.T
-TR...............L..T
-T........._..*...R..T
-TR..Rx~...R*....__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>36</t>
@@ -1706,20 +1263,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTT
-T..~...*........~...T
-T...+R..R..R........T
-T.......R..R........T
-T............L......T
-TR......R..R........T
-T........RR..*......T
-TR..Rx~....*R...__~.T
-T..*Rx.....+T.......T
-T...T.R........*...RT
-TTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>37</t>
   </si>
   <si>
@@ -1739,20 +1282,6 @@
 a</t>
   </si>
   <si>
-    <t>NO CLEAR
-.....................
-...~...*........~....
-....+R..R............
-........R.....R......
-......R..R.R..R...R..
-.R...................
-.........._..*.......
-.R..Rx~...R*....__~..
-...*Rx.....+T........
-......R...........L.R
-.....................</t>
-  </si>
-  <si>
     <t>38</t>
   </si>
   <si>
@@ -1778,20 +1307,6 @@
 d
 d
 d</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-.....................
-...~...*........~....
-....+R..R............
-........R.....R...R..
-......R..R.R..R....LR
-.R...................
-.........._..*.......
-.R..Rx~...R*....__~..
-...*Rx.....+T........
-......R..............
-.....................</t>
   </si>
   <si>
     <t>Tree</t>
@@ -1832,24 +1347,6 @@
 a</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTT
-TTT.T....+....T
-TL.T..T.......T
-T..T........RTT
-T...T..._...T.T
-T..T......_..TT
-T..x...T..T..TT
-TTT...T....T.TT
-TT....T.......T
-T+.T.T.T..T...T
-T..*..T..T.T_.T
-T.T........T.TT
-T.x....T.T.T..T
-TT.T.T..T...T.T
-TTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>40</t>
   </si>
   <si>
@@ -1872,24 +1369,6 @@
 w</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTT
-TTT.T....+....T
-T..T..T.......T
-T..T........RTT
-T...T..._...T.T
-T..T......_..TT
-T..x...T..T..TT
-TTT.L.T....T.TT
-TT....T.......T
-T+...T.T..T...T
-T.....T..T.T_.T
-T.T........T.TT
-T.x....T.T.T..T
-TT.T.T..T...T.T
-TTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
@@ -1903,24 +1382,6 @@
 d
 d
 d</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTT
-TTT.T....+....T
-T..T..T.......T
-T..T........RTT
-T...T..._...T.T
-T....L...._..TT
-T......T..T..TT
-TTT...T....T.TT
-TT....T.......T
-T+.T.T.T..T...T
-T..*..T..T.T_.T
-T.T........T.TT
-T.x....T.T.T..T
-TT.T.T..T...T.T
-TTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>Water</t>
@@ -1957,22 +1418,6 @@
 a</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-TR.R~....T.........T
-T..~~.....~.....*..T
-T..*.........~...R~T
-T.R~.....~R...~.~.~T
-T.R~RR...R...T..~~.T
-TR.~..+.R~....~..R.T
-TR.T.T~R.x.T....~T.T
-T.~~R...R~...~.~~.~T
-T..T..RT..~...~.*.TT
-T..R...xR*~T.._~~.RT
-T.~.~...R.~+T~.T~..T
-TTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>43</t>
   </si>
   <si>
@@ -1999,22 +1444,6 @@
 a
 a
 s</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-TR.R~....T.........T
-T..~~.....~.....*..T
-T..*.........~...R~T
-T.R~....L_....~.~.~T
-T.R~RR...R...T..~~.T
-TR.~..+.R~....~..R.T
-TR.T.T~R.x.T....~T.T
-T.~~R...R~...~.~~.~T
-T..T..RT..~...~.*.TT
-T..R...xR*~T.._~~.RT
-T.~.~...R.~+T~.T~..T
-TTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>44</t>
@@ -2210,23 +1639,6 @@
 s
 w
 w</t>
-  </si>
-  <si>
-    <t>CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTT
-T.......................T
-T.......................T
-T.......................T
-T.......................T
-TTTTTT..................T
-T~~~~T..................T
-T...~TTTTTT.............T
-T...______..............T
-T...~TTTTTT.............T
-T~_~~T..............R...T
-T....T..................T
-T.L..T..................T
-TTTTTTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>Entity</t>
@@ -2271,24 +1683,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTT
-T.....*.+.TR....~.T..T
-T....T.T+..*T++TT*T..T
-T..x.+T.T..Rx...TT..TT
-T.RT.......T.....+R~TT
-TT.x._+..T...~T..T...T
-T+.T.~x.....R....R.RRT
-T...T..R.R_R....T....T
-T....L.R+T...T....~..T
-T.......+.__......_..T
-T..~~....T..*........T
-T..~......T.T.T_.T...T
-T...T.RT...T....TR...T
-T..T.R...R...RTR...TRT
-TTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>46</t>
   </si>
   <si>
@@ -2307,24 +1701,6 @@
 pppppppppp</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTT
-T.....*.+.TR....~.T..T
-T....T.T+..*T++TT*T..T
-T..x.+T.T..Rx...TT..TT
-T.RT.......T.....+R~TT
-TT.x._+..T...~T..T...T
-T+.T.~x.....R....R.RRT
-T...T..R.R_R....T....T
-T......R+T...T....~..T
-.L......+.__......_..T
-T..~~....T..*........T
-T..~......T.T.T_.T...T
-T...T.RT...T....TR...T
-T..T.R...R...RTR...TRT
-TTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>47</t>
   </si>
   <si>
@@ -2346,24 +1722,6 @@
 aa
 s
 s</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTT
-T.....*.+.TR....~.T..T
-T....T.T+..*T++TT*T..T
-T..x.+T.T..Rx...TT..TT
-T.RT.....L.T.....+R~TT
-TT.x._+..T...~T..T...T
-T+.T.~......R....R.RRT
-T...T..R.R_R....T....T
-T......R+T...T....~..T
-T.......+.__......_..T
-Tx.~~....T..*........T
-T..~......T.T.T_.T...T
-T...T.RT...T....TR...T
-T..T.R...R...RTR...TRT
-TTTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>Grid</t>
@@ -2390,19 +1748,6 @@
   <si>
     <t>d
 d</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTT
-T..T..~..T
-T.*..T...T
-T.T..~..+T
-T....R...T
-T.x.+..*.T
-TT...L*RxT
-T..TT...TT
-T.._~..T.T
-TTTTTTTTTT</t>
   </si>
   <si>
     <t>49</t>
@@ -2441,29 +1786,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTT
-TR.....T.T
-T.++.*...T
-T..TTT.~.T
-T_TT.....T
-T+....T.TT
-T~~.xxT.*T
-T.....+..T
-T.....R..T
-T.R_xT...T
-T...*....T
-TT..T.T..T
-T.._.R~.+T
-Tx....T_.T
-T.......TT
-TR...+.R.T
-T..RR....T
-T..R..x..T
-T+~.L..R.T
-TTTTTTTTTT</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
@@ -2487,19 +1809,6 @@
 d</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T..LT.+.RTx..~.....T
-T.T~...~T.T..x._.RxT
-TT.~*..TT+...+.~.+.T
-T..T.T...+..T..*...T
-T..+....~x+xR..R...T
-TTT+...Rx.R.._R....T
-T......*T..*.x.R..*T
-TT.T.T..R~R.TT.R..TT
-TTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>51</t>
   </si>
   <si>
@@ -2512,12 +1821,6 @@
 TTT</t>
   </si>
   <si>
-    <t>CLEAR
-TTT
-TLT
-TTT</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
@@ -2525,12 +1828,6 @@
   </si>
   <si>
     <t>3 4
-TTTT
-T.LT
-TTTT</t>
-  </si>
-  <si>
-    <t>CLEAR
 TTTT
 T.LT
 TTTT</t>
@@ -2655,22 +1952,6 @@
 s</t>
   </si>
   <si>
-    <t>CLEAR
-....................
-..x...R_......R.....
-....T..R............
-.......TRR..~.._....
-.L...x......RTRR....
-.R.._.......x.......
-.RxR..R.R.....*.....
-.*.T..*TR.....R.....
-.....*..............
-...*~~..............
-..x..R..............
-.*..R*..............
-....................</t>
-  </si>
-  <si>
     <t>55</t>
   </si>
   <si>
@@ -2720,22 +2001,6 @@
 ddd
 d
 d</t>
-  </si>
-  <si>
-    <t>CLEAR
-TTTTT~TTTTTTTTTTTTTT
-T....~..~..........T
-T.......T..........T
-T.......T..........T
-T.......T..........T
-T............L.....T
-T.......T..........T
-T.......T..........T
-T.......T..........T
-T.......T..........T
-T.......T..........T
-T....~..~..........T
-TTTTT~TTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>56</t>
@@ -2808,26 +2073,6 @@
 a
 w
 w</t>
-  </si>
-  <si>
-    <t>CLEAR
-TTTTTTTTTTTTTTT
-T.......T.....T
-T.T.T.T.T.T.T.T
-T.T.......T...T
-T.T.T.T.T.T.T.T
-T.T...........T
-T.T.T.T.T.T.TTT
-T.T.....T.....T
-T.TTT.T.T.T.T.T
-T.....T.......T
-T.T.T.TTT.TTT.T
-T.T...........T
-T~~.T.T.T.T.T.T
-TL~.T.........T
-T.T.T.T.T.T.T.T
-T._.........T.T
-TTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>57</t>
@@ -3209,29 +2454,6 @@
 ssss</t>
   </si>
   <si>
-    <t>NO CLEAR
-..............................
-...._....._...................
-..._TTT.R....~.T_.R....x.TT...
-..*T..~T.....~..T.TT...x...T..
-.~.............TR....~.T...T..
-...R...*....T....~T....R_.xTx.
-..T._R..._._.....*TR........~.
-....R_.....T.T.......T_....T..
-.....T..__....~_~...~T........
-..T.........xRT.R*R...........
-....T....R....T.......T.RR....
-..T_.RRRR......*T..T..T.R+....
-._...T_.......T.R.....R.RR....
-..R*xR_....T.x...*.xT~.T..._..
-....*..x._T...*~..............
-...RxT~....~..TT....T......Tx.
-..RT..._...T_.........._......
-...T*...*.T...RT....x.........
-.R...._........_..............
-..............................</t>
-  </si>
-  <si>
     <t>Input Validation</t>
   </si>
   <si>
@@ -3267,29 +2489,6 @@
     <t>WWASSDDD</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
-T.R.R........~.x.~T...TTR....T
-T...+R.*..*T.T.....R+......+.T
-TR.....~.....x..+....+..T....T
-TR.T.........x........R..~_R.T
-T....T.~.R..TT...........T..TT
-T...RTT..+*..*+...++~+..T.TRxT
-T.*..T...R........R..........T
-T.T...T.*+...~~+T.T.x........T
-T_+..LT*.R..~......T..xTRT.x.T
-T...T.*..........._.x...T...TT
-T......_.R.T.......TTR_.T...TT
-T.T........~..Tx..T~T.R..~..TT
-T....._.RT.T..+.xT...Tx.TT...T
-T...T...._T~...TTT...R.*.....T
-T...~..RRT...T..~.*TT.+..*..TT
-TT.....*R..+~..T..~T.....TT..T
-T.+....T*T......RT*...T~...T.T
-T.T.T....T.R.++.xRT....R..T~.T
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>should do after all tests</t>
   </si>
   <si>
@@ -3311,29 +2510,6 @@
     <t>wWaSsDdsssaAawSWsD</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
-T.R.R........~.x.~T...TTR....T
-T...+R.*..*T.T.....R+......+.T
-TR.....~.....x..+....+..T....T
-TR.T.........x........R..~_R.T
-T....T.~.R..TT...........T..TT
-T...RTT..+*..*+...++~+..T.TRxT
-T.*..T...R........R..........T
-T.T...T.*+...~~+T.T.x........T
-T_+...T*.R..~......T..xTRT.x.T
-T...T.*..........._.x...T...TT
-T......_.R.T.......TTR_.T...TT
-T.T.L......~..Tx..T~T.R..~..TT
-T....._.RT.T..+.xT...Tx.TT...T
-T...T...._T~...TTT...R.*.....T
-T...~..RRT...T..~.*TT.+..*..TT
-TT.....*R..+~..T..~T.....TT..T
-T.+....T*T......RT*...T~...T.T
-T.T.T....T.R.++.xRT....R..T~.T
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>61</t>
   </si>
   <si>
@@ -3341,29 +2517,6 @@
   </si>
   <si>
     <t>jinn</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
-T.R.R........~.x.~T...TTR....T
-T...+R.*..*T.T.....R+......+.T
-TR.....~.....x..+....+..T....T
-TR.T.........x........R..~_R.T
-T....T.~.R..TT...........T..TT
-T...RTT..+*..*+...++~+..T.TRxT
-T.*..T...R........R..........T
-T.T...T.*+...~~+T.T.x........T
-T_+.L.T*.R..~......T..xTRT.x.T
-T...T.*..........._.x...T...TT
-T......_.R.T.......TTR_.T...TT
-T.T........~..Tx..T~T.R..~..TT
-T....._.RT.T..+.xT...Tx.TT...T
-T...T...._T~...TTT...R.*.....T
-T...~..RRT...T..~.*TT.+..*..TT
-TT.....*R..+~..T..~T.....TT..T
-T.+....T*T......RT*...T~...T.T
-T.T.T....T.R.++.xRT....R..T~.T
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>62</t>
@@ -3393,29 +2546,6 @@
 a</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
-T.R.R........~.x.~T...TTR....T
-T...+R.*..*T.T.....R+......+.T
-TR.....~.....x..+....+..T....T
-TR.T.........x........R..~_R.T
-T....T.~.R..TT...........T..TT
-T...RTT..+*..*+...++~+..T.TRxT
-T.*..T...R........R..........T
-T.T...T.*+...~~+T.T.x........T
-T_+...T*.R..~......T..xTRT.x.T
-T.L.T.*..........._.x...T...TT
-T......_.R.T.......TTR_.T...TT
-T.T........~..Tx..T~T.R..~..TT
-T....._.RT.T..+.xT...Tx.TT...T
-T...T...._T~...TTT...R.*.....T
-T...~..RRT...T..~.*TT.+..*..TT
-TT.....*R..+~..T..~T.....TT..T
-T.+....T*T......RT*...T~...T.T
-T.T.T....T.R.++.xRT....R..T~.T
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>64</t>
   </si>
   <si>
@@ -3442,29 +2572,6 @@
 ssWssWssW</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
-T.R.R........~.x.~T...TTR....T
-T...+R.*..*T.T.....R+......+.T
-TR.....~.....x..+....+..T....T
-TR.T.........x........R..~_R.T
-T....T.~.R..TT...........T..TT
-T...RTT..+*..*+...++~+..T.TRxT
-T.*..T...R........R..........T
-T.T...T.*+...~~+T.T.x........T
-T_+...T*.R..~......T..xTRT.x.T
-T...T.*..........._.x...T...TT
-T......_.R.T.......TTR_.T...TT
-T.TL.......~..Tx..T~T.R..~..TT
-T....._.RT.T..+.xT...Tx.TT...T
-T...T...._T~...TTT...R.*.....T
-T...~..RRT...T..~.*TT.+..*..TT
-TT.....*R..+~..T..~T.....TT..T
-T.+....T*T......RT*...T~...T.T
-T.T.T....T.R.++.xRT....R..T~.T
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>66</t>
   </si>
   <si>
@@ -3477,29 +2584,6 @@
 water is wet
 those who know
 the secret to life is: WWWWWWWWWWWWWWWWWWWWWWW</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
-T.R.R........~.x.~T...TTR....T
-T...+R.*..*T.T.....R+......+.T
-TR.....~.....x..+....+..T....T
-TR.T.........x........R..~_R.T
-T....T.~.R..TT...........T..TT
-T...RTT..+*..*+...++~+..T.TRxT
-T.*..T...R........R..........T
-T.TL..T.*+...~~+T.T.x........T
-T_+...T*.R..~......T..xTRT.x.T
-T...T.*..........._.x...T...TT
-T......_.R.T.......TTR_.T...TT
-T.T........~..Tx..T~T.R..~..TT
-T....._.RT.T..+.xT...Tx.TT...T
-T...T...._T~...TTT...R.*.....T
-T...~..RRT...T..~.*TT.+..*..TT
-TT.....*R..+~..T..~T.....TT..T
-T.+....T*T......RT*...T~...T.T
-T.T.T....T.R.++.xRT....R..T~.T
-TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>67</t>
@@ -3523,18 +2607,6 @@
     <t>wwaaaaaaaaaaaaaaaaaaaaaaaaaaaa</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T..................T
-T..................T
-T.....~....+.+.....T
-T.....~......+.....T
-T.....~............T
-T..................T
-T..................T
-TTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>68</t>
   </si>
   <si>
@@ -3542,18 +2614,6 @@
   </si>
   <si>
     <t>wwwwwwwwwwwwwwwddsssssssssssssssssssss</t>
-  </si>
-  <si>
-    <t>CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T..................T
-T..................T
-T.....~............T
-T.....~......L.....T
-T.....~............T
-T..................T
-T..................T
-TTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>69</t>
@@ -3567,18 +2627,6 @@
 ww</t>
   </si>
   <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T..................T
-T..................T
-T.....~....+.+.....T
-T.....~....L.+.....T
-T.....~............T
-T..................T
-T..................T
-TTTTTTTTTTTTTTTTTTTT</t>
-  </si>
-  <si>
     <t>I don't know the expected output of this</t>
   </si>
   <si>
@@ -3607,18 +2655,6 @@
   <si>
     <t>ww!
 aaaaaaaaaaaaaaa</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T..................T
-T..................T
-T.....~....+.+.....T
-T.....~......+.....T
-T.....~............T
-TL.................T
-T..................T
-TTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>Game Logic</t>
@@ -3646,19 +2682,6 @@
     <t>wapwwwwwdddddddddddddddddddddddddddddddddsaaaaaaaaaaaaaaaaaaadwaasssssssssssssssssssssssssss</t>
   </si>
   <si>
-    <t>NO CLEAR
-.................L..
-..~...........R.RR..
-............._...R..
-..T...*..x.....T.*..
-...~....*+...._.....
-.R........._.T......
-........x..+.....Tx.
-...R+.*._.+.........
-.......*+.R....+....
-....................</t>
-  </si>
-  <si>
     <t>74</t>
   </si>
   <si>
@@ -3666,19 +2689,6 @@
   </si>
   <si>
     <t>ssddwssddsaddsdddddddddddaaaaaaaaaaaaaaaaaaaaaaaaaaaaaawaaswaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa</t>
-  </si>
-  <si>
-    <t>CLEAR
-TTTTTTTTTTTTTTTTTTTT
-T.~..........TR.R.RT
-T.....*......_...R.T
-T.T...*..x.....T.*.T
-T..~....*....._....T
-TR........._.T.....T
-T.......x........TxT
-T..RL.*._..........T
-T......*.R.........T
-TTTTTTTTTTTTTTTTTTTT</t>
   </si>
   <si>
     <t>75</t>
@@ -3723,7 +2733,1112 @@
     <t>wwwwwwwwwwwwwwwwwpddddddddddddddddddddddddddddddwapwwwwwwwwwwwwwwwwwwwwwwwsaaaaaaaaaawaaaasaaaaawawwpaaaaasaaaaaaaaaawdssssssssssssssssssssssssssssssssasssssssssssssssssdddwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwwassssssssssssassdddddddddddddddwwdaawwdddwwwwddsssaddddWddwwDDDDDsswaaswddsssdddwdDDDDDDDDDDaaasssssssssssssssssssssssssssswwaaaadwssaaasaaawawaasaaaawwwwaasaaassssssssdddwsaaaaawwwWWWWWWWWWaWWWWWWdswdddSsddaSwAAAAAAAAAAAAAAAAwwwwwwwwwwwwwwwwDDDDDdsaaWWWWDDDDDDDDDDDsawasswdddssaddddsawasswaaasasasssddwaasawwdwasawWWsaawawaasdaaassdsdwwawddaassdddawwawddddddssssssssasdsdwawdddddwwwwwwdwwdwwassdddddddddddddpaaaaassswwwwwdddsdpaasssssssWWWWAAAAAAADDDDDDDDDDDD</t>
   </si>
   <si>
-    <t>CLEAR
+    <t>Date Added</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>10x20</t>
+  </si>
+  <si>
+    <t>Miscellaneous</t>
+  </si>
+  <si>
+    <t>Reset immediately after win</t>
+  </si>
+  <si>
+    <t>Water death preventing win</t>
+  </si>
+  <si>
+    <t>10 10
+TTTTTTTTTT
+T......+.T
+T........T
+T.L....~.T
+TTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>dddddww</t>
+  </si>
+  <si>
+    <t>wwddddd!</t>
+  </si>
+  <si>
+    <t>Attempt to move after reset in the same string (should still run)</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x..*.L.T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x..*..LT
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~..T
+T.*.._.....x..*..LT
+T.......R....R*..RT
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTLTTTTTT
+T....+R..T+.......T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x..*...T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x......T
+T.......R....R*...T
+T..........._.*L.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+....L..............
+.....+R...+....x...
+.~...x*._..R.......
+..~_.*...+.....~.R.
+..*.._.....x.......
+........R....R*....
+............_.*T.R.
+.R._.~..R.x*...RR..
+.R....~..._........
+...................</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+..................L
+.....+R...+....x...
+.~...x*._..R.......
+..~_.*...+.....~.R.
+..*.._.....x.......
+........R....R*....
+............_.*T.R.
+.R._.~..R.x*...RR..
+.R....~..._........
+...................</t>
+  </si>
+  <si>
+    <t>10 19
+CLEAR
+...................
+......R........x...
+.~...x*R_..........
+..~_.*...L.....~.R.
+..*.._.....x..*....
+............RR*....
+............_.*T.R.
+.R._.~..R......RR..
+.R....~..._........
+...................</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T.....x..T
+T~...x*._.LR......T
+TT~_.*...+.....~.RT
+T.*.._.....x..*...T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....LR..T.....x..T
+T~...x*._..R......T
+TT~_.*.........~.RT
+T.*.._.....x..*...T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+...................
+.....+R...+....x...
+.~...x*._..R.......
+..~_.*...+.....~.R.
+..*.._.....x....L..
+........R....R*....
+............_.*T.R.
+.R._.~..R.x*...RR..
+.R....~..._........
+...................</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x......T
+T.......R....R*...T
+T..........._.*.LRT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+...................
+.....+R...+...Lx...
+.~...x*._..R.......
+..~_.*...+.....~.R.
+..*.._.....x.......
+........R....R*....
+............_.*T.R.
+.R._.~..R.x*...RR..
+.R....~..._........
+...................</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x......T
+T.......R....R*..LT
+T..........._.*..RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+...................
+.....+R...+....x...
+.~...x*._..R.......
+..~_.*...+.....~.R.
+..*.._.....x.......
+........R....R....L
+............_.*..R.
+.R._.~..R.x*...RR..
+.R....~..._........
+...................</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....xL.....T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+R...x..T
+T~...x*._..L......T
+TT~_.*...+.....~.RT
+T.*.._.....x......T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+....x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x...L..T
+T.......R....R*...T
+T..........._.*T.RT
+TR._.~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T.....R..T.....x..T
+T~...x*._..R......T
+TT~_.*.........~.RT
+T.*.._.....x..*...T
+T..~~~..R....R*...T
+T..~+~......_.*T.RT
+TR.~~~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+CLEAR
+TTTTTTTTTTTTTTTTTTT
+T.....R..T.....x..T
+T~...x*._..R......T
+TT~_.*.........~.RT
+T.*.._.....x..*...T
+T..~~~.......R*...T
+T..~L_......_.*T.RT
+TR.~~~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 19
+NO CLEAR
+TTTTTTTTTTTTTTTTTTT
+T....+R..T+.L..x..T
+T~...x*._..R......T
+TT~_.*...+.....~.RT
+T.*.._.....x..*...T
+T..~~~..R....R*...T
+T..~+~......_.*T.RT
+TR.~~~..R.x*...RR.T
+TR....~T.T_.......T
+TTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>14 25
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTT
+T..x....T.R.._..+T~.....T
+T.T.....~.R........T.+.~T
+T...T.Tx....~.....R.T..*T
+T.....*....T...T.T..~.TTT
+T.......T....+....._~._.T
+T....~....+......R......T
+T*.T..__...___.L..~_.*~.T
+T.x....+..R.T.........T.T
+T....+_....+.......T.T.TT
+T_T..........T.._T.....*T
+T.....+...*R~...*...+...T
+T........T...+TxR.T...T.T
+TTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>14 25
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTT
+T..x....T.R.._..+T~.....T
+T.T.....~.R........T.+.~T
+T...T.Tx....~.....R.T..*T
+T.....*....T...T.T..~.TTT
+T.......T....+....._~._.T
+T....~....+........L....T
+T*.T..__...___....__.*~.T
+T.x....+..R.T.........T.T
+T....+_....+.......T.T.TT
+T_T..........T.._T.....*T
+T.....+...*R~...*...+...T
+T........T...+TxR.T...T.T
+TTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>14 25
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTT
+T..x....T.R.._..+T~.....T
+T.T.....~..........T.+.~T
+T...T.Tx....~.......T..*T
+T.....*....T...T.T.._.TTT
+T.......T....+.....__._.T
+T....~....+.............T
+T*.T..__...___....__L*~.T
+T.x....+..R.T.........T.T
+T....+_....+.......T.T.TT
+T_T..........T.._T.....*T
+T.....+...*R~...*...+...T
+T........T...+TxR.T...T.T
+TTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>14 25
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTT
+T..x....T.R.._..+T~.....T
+T.T.....~.R........T.+.~T
+T...T.Tx....~.....R.T..*T
+T.....*....T...T.T..~.TTT
+T..L....T....+....._~._.T
+T....~....+......R......T
+T*....__...___....~_.*~.T
+T......+..R.T.........T.T
+T....+_....+.......T.T.TT
+T_T..........T.._T.....*T
+T.....+...*R~...*...+...T
+T........T...+TxR.T...T.T
+TTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>14 25
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTT
+T..x....T.R.._..+T~.....T
+T.T.....~.R........T.+.~T
+T...T.Tx....~.....R.T..*T
+T.....*....T...T.T..~.LTT
+T.......T....+....._~._.T
+T....~....+......R......T
+T*.T..__...___....~_.*~.T
+T......+..R.T.........T.T
+T....+_....+.......T.T.TT
+T_T..........T.._T.....*T
+T.....+...*R~...*...+...T
+T........T...+TxR.T...T.T
+TTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R...........T
+T.......R.....R.....T
+T.....R..R....R...R.T
+TR..........L.......T
+T........._..*......T
+TR..Rx~...R*R...__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R...........T
+T.......R.....RRL...T
+T.....R..R.R......R.T
+TR..................T
+T........._..*......T
+TR..Rx~...R*....__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R...........T
+T...R...R.....R.....T
+T...L....R.R..R...R.T
+TR..................T
+T........._..*......T
+TR..Rx~...R*....__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R...........T
+T.......R.....R.....T
+T....L...R.R..R...R.T
+TR..................T
+T....R...._..*......T
+TR..Rx~...R*....__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R.....R.....T
+T.......R....L......T
+T.....R..R.R......R.T
+TR...........R......T
+T........._..*......T
+TR..Rx~...R*....__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R...........T
+T.......R...........T
+T.....R..R.R.R....R.T
+TR..................T
+T........._..*......T
+TR..Rx~...R*..L.R_~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R...........T
+T.......R.....R.....T
+T.....R..R.R......R.T
+TR...............L..T
+T........._..*...R..T
+TR..Rx~...R*....__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTT
+T..~...*........~...T
+T...+R..R..R........T
+T.......R..R........T
+T............L......T
+TR......R..R........T
+T........RR..*......T
+TR..Rx~....*R...__~.T
+T..*Rx.....+T.......T
+T...T.R........*...RT
+TTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+.....................
+...~...*........~....
+....+R..R............
+........R.....R......
+......R..R.R..R...R..
+.R...................
+.........._..*.......
+.R..Rx~...R*....__~..
+...*Rx.....+T........
+......R...........L.R
+.....................</t>
+  </si>
+  <si>
+    <t>11 21
+NO CLEAR
+.....................
+...~...*........~....
+....+R..R............
+........R.....R...R..
+......R..R.R..R....LR
+.R...................
+.........._..*.......
+.R..Rx~...R*....__~..
+...*Rx.....+T........
+......R..............
+.....................</t>
+  </si>
+  <si>
+    <t>15 15
+NO CLEAR
+TTTTTTTTTTTTTTT
+TTT.T....+....T
+TL.T..T.......T
+T..T........RTT
+T...T..._...T.T
+T..T......_..TT
+T..x...T..T..TT
+TTT...T....T.TT
+TT....T.......T
+T+.T.T.T..T...T
+T..*..T..T.T_.T
+T.T........T.TT
+T.x....T.T.T..T
+TT.T.T..T...T.T
+TTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>15 15
+NO CLEAR
+TTTTTTTTTTTTTTT
+TTT.T....+....T
+T..T..T.......T
+T..T........RTT
+T...T..._...T.T
+T..T......_..TT
+T..x...T..T..TT
+TTT.L.T....T.TT
+TT....T.......T
+T+...T.T..T...T
+T.....T..T.T_.T
+T.T........T.TT
+T.x....T.T.T..T
+TT.T.T..T...T.T
+TTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>15 15
+NO CLEAR
+TTTTTTTTTTTTTTT
+TTT.T....+....T
+T..T..T.......T
+T..T........RTT
+T...T..._...T.T
+T....L...._..TT
+T......T..T..TT
+TTT...T....T.TT
+TT....T.......T
+T+.T.T.T..T...T
+T..*..T..T.T_.T
+T.T........T.TT
+T.x....T.T.T..T
+TT.T.T..T...T.T
+TTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>13 20
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTT
+TR.R~....T.........T
+T..~~.....~.....*..T
+T..*.........~...R~T
+T.R~.....~R...~.~.~T
+T.R~RR...R...T..~~.T
+TR.~..+.R~....~..R.T
+TR.T.T~R.x.T....~T.T
+T.~~R...R~...~.~~.~T
+T..T..RT..~...~.*.TT
+T..R...xR*~T.._~~.RT
+T.~.~...R.~+T~.T~..T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>13 20
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTT
+TR.R~....T.........T
+T..~~.....~.....*..T
+T..*.........~...R~T
+T.R~....L_....~.~.~T
+T.R~RR...R...T..~~.T
+TR.~..+.R~....~..R.T
+TR.T.T~R.x.T....~T.T
+T.~~R...R~...~.~~.~T
+T..T..RT..~...~.*.TT
+T..R...xR*~T.._~~.RT
+T.~.~...R.~+T~.T~..T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>14 25
+CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTT
+T.......................T
+T.......................T
+T.......................T
+T.......................T
+TTTTTT..................T
+T~~~~T..................T
+T...~TTTTTT.............T
+T...______..............T
+T...~TTTTTT.............T
+T~_~~T..............R...T
+T....T..................T
+T.L..T..................T
+TTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>15 22
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTT
+T.....*.+.TR....~.T..T
+T....T.T+..*T++TT*T..T
+T..x.+T.T..Rx...TT..TT
+T.RT.......T.....+R~TT
+TT.x._+..T...~T..T...T
+T+.T.~x.....R....R.RRT
+T...T..R.R_R....T....T
+T....L.R+T...T....~..T
+T.......+.__......_..T
+T..~~....T..*........T
+T..~......T.T.T_.T...T
+T...T.RT...T....TR...T
+T..T.R...R...RTR...TRT
+TTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>15 22
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTT
+T.....*.+.TR....~.T..T
+T....T.T+..*T++TT*T..T
+T..x.+T.T..Rx...TT..TT
+T.RT.......T.....+R~TT
+TT.x._+..T...~T..T...T
+T+.T.~x.....R....R.RRT
+T...T..R.R_R....T....T
+T......R+T...T....~..T
+.L......+.__......_..T
+T..~~....T..*........T
+T..~......T.T.T_.T...T
+T...T.RT...T....TR...T
+T..T.R...R...RTR...TRT
+TTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>15 22
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTT
+T.....*.+.TR....~.T..T
+T....T.T+..*T++TT*T..T
+T..x.+T.T..Rx...TT..TT
+T.RT.....L.T.....+R~TT
+TT.x._+..T...~T..T...T
+T+.T.~......R....R.RRT
+T...T..R.R_R....T....T
+T......R+T...T....~..T
+T.......+.__......_..T
+Tx.~~....T..*........T
+T..~......T.T.T_.T...T
+T...T.RT...T....TR...T
+T..T.R...R...RTR...TRT
+TTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 10
+NO CLEAR
+TTTTTTTTTT
+T..T..~..T
+T.*..T...T
+T.T..~..+T
+T....R...T
+T.x.+..*.T
+TT...L*RxT
+T..TT...TT
+T.._~..T.T
+TTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 10
+NO CLEAR
+TTTTTTTTTT
+TR.....T.T
+T.++.*...T
+T..TTT.~.T
+T_TT.....T
+T+....T.TT
+T~~.xxT.*T
+T.....+..T
+T.....R..T
+T.R_xT...T
+T...*....T
+TT..T.T..T
+T.._.R~.+T
+Tx....T_.T
+T.......TT
+TR...+.R.T
+T..RR....T
+T..R..x..T
+T+~.L..R.T
+TTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 20
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTT
+T..LT.+.RTx..~.....T
+T.T~...~T.T..x._.RxT
+TT.~*..TT+...+.~.+.T
+T..T.T...+..T..*...T
+T..+....~x+xR..R...T
+TTT+...Rx.R.._R....T
+T......*T..*.x.R..*T
+TT.T.T..R~R.TT.R..TT
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>3 3
+CLEAR
+TTT
+TLT
+TTT</t>
+  </si>
+  <si>
+    <t>3 4
+CLEAR
+TTTT
+T.LT
+TTTT</t>
+  </si>
+  <si>
+    <t>13 20
+CLEAR
+....................
+..x...R_......R.....
+....T..R............
+.......TRR..~.._....
+.L...x......RTRR....
+.R.._.......x.......
+.RxR..R.R.....*.....
+.*.T..*TR.....R.....
+.....*..............
+...*~~..............
+..x..R..............
+.*..R*..............
+....................</t>
+  </si>
+  <si>
+    <t>13 20
+CLEAR
+TTTTT~TTTTTTTTTTTTTT
+T....~..~..........T
+T.......T..........T
+T.......T..........T
+T.......T..........T
+T............L.....T
+T.......T..........T
+T.......T..........T
+T.......T..........T
+T.......T..........T
+T.......T..........T
+T....~..~..........T
+TTTTT~TTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>17 15
+CLEAR
+TTTTTTTTTTTTTTT
+T.......T.....T
+T.T.T.T.T.T.T.T
+T.T.......T...T
+T.T.T.T.T.T.T.T
+T.T...........T
+T.T.T.T.T.T.TTT
+T.T.....T.....T
+T.TTT.T.T.T.T.T
+T.....T.......T
+T.T.T.TTT.TTT.T
+T.T...........T
+T~~.T.T.T.T.T.T
+TL~.T.........T
+T.T.T.T.T.T.T.T
+T._.........T.T
+TTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+..............................
+...._....._...................
+..._TTT.R....~.T_.R....x.TT...
+..*T..~T.....~..T.TT...x...T..
+.~.............TR....~.T...T..
+...R...*....T....~T....R_.xTx.
+..T._R..._._.....*TR........~.
+....R_.....T.T.......T_....T..
+.....T..__....~_~...~T........
+..T.........xRT.R*R...........
+....T....R....T.......T.RR....
+..T_.RRRR......*T..T..T.R+....
+._...T_.......T.R.....R.RR....
+..R*xR_....T.x...*.xT~.T..._..
+....*..x._T...*~..............
+...RxT~....~..TT....T......Tx.
+..RT..._...T_.........._......
+...T*...*.T...RT....x.........
+.R...._........_..............
+..............................</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
+T.R.R........~.x.~T...TTR....T
+T...+R.*..*T.T.....R+......+.T
+TR.....~.....x..+....+..T....T
+TR.T.........x........R..~_R.T
+T....T.~.R..TT...........T..TT
+T...RTT..+*..*+...++~+..T.TRxT
+T.*..T...R........R..........T
+T.T...T.*+...~~+T.T.x........T
+T_+..LT*.R..~......T..xTRT.x.T
+T...T.*..........._.x...T...TT
+T......_.R.T.......TTR_.T...TT
+T.T........~..Tx..T~T.R..~..TT
+T....._.RT.T..+.xT...Tx.TT...T
+T...T...._T~...TTT...R.*.....T
+T...~..RRT...T..~.*TT.+..*..TT
+TT.....*R..+~..T..~T.....TT..T
+T.+....T*T......RT*...T~...T.T
+T.T.T....T.R.++.xRT....R..T~.T
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
+T.R.R........~.x.~T...TTR....T
+T...+R.*..*T.T.....R+......+.T
+TR.....~.....x..+....+..T....T
+TR.T.........x........R..~_R.T
+T....T.~.R..TT...........T..TT
+T...RTT..+*..*+...++~+..T.TRxT
+T.*..T...R........R..........T
+T.T...T.*+...~~+T.T.x........T
+T_+...T*.R..~......T..xTRT.x.T
+T...T.*..........._.x...T...TT
+T......_.R.T.......TTR_.T...TT
+T.T.L......~..Tx..T~T.R..~..TT
+T....._.RT.T..+.xT...Tx.TT...T
+T...T...._T~...TTT...R.*.....T
+T...~..RRT...T..~.*TT.+..*..TT
+TT.....*R..+~..T..~T.....TT..T
+T.+....T*T......RT*...T~...T.T
+T.T.T....T.R.++.xRT....R..T~.T
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
+T.R.R........~.x.~T...TTR....T
+T...+R.*..*T.T.....R+......+.T
+TR.....~.....x..+....+..T....T
+TR.T.........x........R..~_R.T
+T....T.~.R..TT...........T..TT
+T...RTT..+*..*+...++~+..T.TRxT
+T.*..T...R........R..........T
+T.T...T.*+...~~+T.T.x........T
+T_+.L.T*.R..~......T..xTRT.x.T
+T...T.*..........._.x...T...TT
+T......_.R.T.......TTR_.T...TT
+T.T........~..Tx..T~T.R..~..TT
+T....._.RT.T..+.xT...Tx.TT...T
+T...T...._T~...TTT...R.*.....T
+T...~..RRT...T..~.*TT.+..*..TT
+TT.....*R..+~..T..~T.....TT..T
+T.+....T*T......RT*...T~...T.T
+T.T.T....T.R.++.xRT....R..T~.T
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
+T.R.R........~.x.~T...TTR....T
+T...+R.*..*T.T.....R+......+.T
+TR.....~.....x..+....+..T....T
+TR.T.........x........R..~_R.T
+T....T.~.R..TT...........T..TT
+T...RTT..+*..*+...++~+..T.TRxT
+T.*..T...R........R..........T
+T.T...T.*+...~~+T.T.x........T
+T_+...T*.R..~......T..xTRT.x.T
+T.L.T.*..........._.x...T...TT
+T......_.R.T.......TTR_.T...TT
+T.T........~..Tx..T~T.R..~..TT
+T....._.RT.T..+.xT...Tx.TT...T
+T...T...._T~...TTT...R.*.....T
+T...~..RRT...T..~.*TT.+..*..TT
+TT.....*R..+~..T..~T.....TT..T
+T.+....T*T......RT*...T~...T.T
+T.T.T....T.R.++.xRT....R..T~.T
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
+T.R.R........~.x.~T...TTR....T
+T...+R.*..*T.T.....R+......+.T
+TR.....~.....x..+....+..T....T
+TR.T.........x........R..~_R.T
+T....T.~.R..TT...........T..TT
+T...RTT..+*..*+...++~+..T.TRxT
+T.*..T...R........R..........T
+T.T...T.*+...~~+T.T.x........T
+T_+...T*.R..~......T..xTRT.x.T
+T...T.*..........._.x...T...TT
+T......_.R.T.......TTR_.T...TT
+T.TL.......~..Tx..T~T.R..~..TT
+T....._.RT.T..+.xT...Tx.TT...T
+T...T...._T~...TTT...R.*.....T
+T...~..RRT...T..~.*TT.+..*..TT
+TT.....*R..+~..T..~T.....TT..T
+T.+....T*T......RT*...T~...T.T
+T.T.T....T.R.++.xRT....R..T~.T
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>20 30
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT
+T.R.R........~.x.~T...TTR....T
+T...+R.*..*T.T.....R+......+.T
+TR.....~.....x..+....+..T....T
+TR.T.........x........R..~_R.T
+T....T.~.R..TT...........T..TT
+T...RTT..+*..*+...++~+..T.TRxT
+T.*..T...R........R..........T
+T.TL..T.*+...~~+T.T.x........T
+T_+...T*.R..~......T..xTRT.x.T
+T...T.*..........._.x...T...TT
+T......_.R.T.......TTR_.T...TT
+T.T........~..Tx..T~T.R..~..TT
+T....._.RT.T..+.xT...Tx.TT...T
+T...T...._T~...TTT...R.*.....T
+T...~..RRT...T..~.*TT.+..*..TT
+TT.....*R..+~..T..~T.....TT..T
+T.+....T*T......RT*...T~...T.T
+T.T.T....T.R.++.xRT....R..T~.T
+TTTTTTTTTTTTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 20
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTT
+T..................T
+T..................T
+T.....~....+.+.....T
+T.....~......+.....T
+T.....~............T
+T..................T
+T..................T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 20
+CLEAR
+TTTTTTTTTTTTTTTTTTTT
+T..................T
+T..................T
+T.....~............T
+T.....~......L.....T
+T.....~............T
+T..................T
+T..................T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 20
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTT
+T..................T
+T..................T
+T.....~....+.+.....T
+T.....~....L.+.....T
+T.....~............T
+T..................T
+T..................T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 20
+NO CLEAR
+TTTTTTTTTTTTTTTTTTTT
+T..................T
+T..................T
+T.....~....+.+.....T
+T.....~......+.....T
+T.....~............T
+TL.................T
+T..................T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>10 20
+NO CLEAR
+.................L..
+..~...........R.RR..
+............._...R..
+..T...*..x.....T.*..
+...~....*+...._.....
+.R........._.T......
+........x..+.....Tx.
+...R+.*._.+.........
+.......*+.R....+....
+....................</t>
+  </si>
+  <si>
+    <t>10 20
+CLEAR
+TTTTTTTTTTTTTTTTTTTT
+T.~..........TR.R.RT
+T.....*......_...R.T
+T.T...*..x.....T.*.T
+T..~....*....._....T
+TR........._.T.....T
+T.......x........TxT
+T..RL.*._..........T
+T......*.R.........T
+TTTTTTTTTTTTTTTTTTTT</t>
+  </si>
+  <si>
+    <t>30 30
+CLEAR
 ..............................
 ....._*~..x.x......._......*x.
 .x.xx.R*.~....x.x_........_~R.
@@ -3756,25 +3871,8 @@
 ..............................</t>
   </si>
   <si>
-    <t>Date Added</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>10x20</t>
-  </si>
-  <si>
-    <t>Miscellaneous</t>
-  </si>
-  <si>
-    <t>Reset immediately after win</t>
-  </si>
-  <si>
-    <t>Water death preventing win</t>
-  </si>
-  <si>
     <t>10 10
+NO CLEAR
 TTTTTTTTTT
 T......+.T
 T........T
@@ -3782,29 +3880,13 @@
 TTTTTTTTTT</t>
   </si>
   <si>
-    <t>dddddww</t>
-  </si>
-  <si>
-    <t>wwddddd!</t>
-  </si>
-  <si>
-    <t>NO CLEAR
-TTTTTTTTTT
-T......+.T
-T........T
-T.L....~.T
-TTTTTTTTTT</t>
-  </si>
-  <si>
-    <t>NO CLEAR
+    <t>10 10
+NO CLEAR
 TTTTTTTTTT
 T......+.T
 T........T
 T......~.T
 TTTTTTTTTT</t>
-  </si>
-  <si>
-    <t>Attempt to move after reset in the same string (should still run)</t>
   </si>
 </sst>
 </file>
@@ -4193,7 +4275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="5"/>
@@ -4205,7 +4287,7 @@
     <col min="9" max="16384" width="9.06640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="29.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4228,10 +4310,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -4245,25 +4327,26 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>329</v>
+        <v>262</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -4272,1818 +4355,1894 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>275</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="342" x14ac:dyDescent="0.45">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="342" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>276</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="185.25" x14ac:dyDescent="0.45">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="185.25" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>277</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="213.75" x14ac:dyDescent="0.45">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="327.75" x14ac:dyDescent="0.45">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="327.75" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>281</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>282</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>283</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>284</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="256.5" x14ac:dyDescent="0.45">
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="256.5" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>285</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>286</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="213.75" x14ac:dyDescent="0.45">
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="213.75" x14ac:dyDescent="0.45">
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="270.75" x14ac:dyDescent="0.45">
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="270.75" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="313.5" x14ac:dyDescent="0.45">
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>92</v>
+        <v>289</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>96</v>
+        <v>290</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>101</v>
+        <v>291</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="213.75" x14ac:dyDescent="0.45">
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="228" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>106</v>
+        <v>292</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="399" x14ac:dyDescent="0.45">
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="399" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>110</v>
+        <v>293</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>114</v>
+        <v>294</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="213.75" x14ac:dyDescent="0.45">
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" ht="228" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>119</v>
+        <v>295</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>296</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="270.75" x14ac:dyDescent="0.45">
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" ht="270.75" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" ht="228" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>133</v>
+        <v>298</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="242.25" x14ac:dyDescent="0.45">
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="228" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>141</v>
+        <v>300</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="213.75" x14ac:dyDescent="0.45">
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>145</v>
+        <v>301</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="285" x14ac:dyDescent="0.45">
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" ht="285" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>149</v>
+        <v>302</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="171" x14ac:dyDescent="0.45">
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" ht="185.25" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>161</v>
+        <v>305</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="285" x14ac:dyDescent="0.45">
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" ht="285" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>307</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>177</v>
+        <v>309</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="199.5" x14ac:dyDescent="0.45">
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>183</v>
+        <v>310</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="285" x14ac:dyDescent="0.45">
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" ht="285" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>187</v>
+        <v>311</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>192</v>
+        <v>312</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>198</v>
+        <v>313</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>202</v>
+        <v>314</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="228" x14ac:dyDescent="0.45">
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>217</v>
+        <v>317</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>330</v>
+        <v>263</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>221</v>
+        <v>318</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>225</v>
+        <v>319</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>237</v>
+        <v>187</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>238</v>
+        <v>321</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="384.75" x14ac:dyDescent="0.45">
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9" ht="384.75" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>246</v>
+        <v>194</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>247</v>
+        <v>195</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>248</v>
+        <v>323</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>253</v>
+        <v>324</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>259</v>
+        <v>325</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="H59" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>259</v>
+        <v>325</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="H60" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>264</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>265</v>
+        <v>210</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>266</v>
+        <v>211</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="H61" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>268</v>
+        <v>212</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="H62" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>272</v>
+        <v>215</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="H63" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>275</v>
+        <v>218</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="299.25" x14ac:dyDescent="0.45">
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9" ht="313.5" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>291</v>
+        <v>231</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>299</v>
+        <v>237</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>300</v>
+        <v>238</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>303</v>
+        <v>240</v>
       </c>
       <c r="H70" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>305</v>
+        <v>242</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>339</v>
+        <v>270</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>308</v>
+        <v>245</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>314</v>
+        <v>250</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>315</v>
+        <v>251</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>316</v>
+        <v>252</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>317</v>
+        <v>253</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" ht="171" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>320</v>
+        <v>255</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>316</v>
+        <v>252</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>324</v>
+        <v>258</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>325</v>
+        <v>259</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>326</v>
+        <v>260</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="4">
         <v>45961</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:9" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="B77" s="5">
         <v>76</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>332</v>
+        <v>265</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>334</v>
+        <v>267</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>336</v>
+        <v>269</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H77" s="4">
         <v>45962</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:9" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="B78" s="5">
         <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>333</v>
+        <v>266</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>334</v>
+        <v>267</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>335</v>
+        <v>268</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H78" s="4">
         <v>45962</v>
       </c>
+      <c r="I78" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
